--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128861941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128861815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862614</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862201</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,8 +1385,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128862201</v>
+        <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89035</v>
+        <v>89206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,19 +1173,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4398</v>
+        <v>4393</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Gliophorus psittacinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Herink</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -1238,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,16 +1278,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128862201</t>
+          <t>https://artportalen.se/Sighting/128862137</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128862137</v>
+        <v>128862201</v>
       </c>
       <c r="B7" t="n">
-        <v>89060</v>
+        <v>89035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,11 +1295,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>239221</v>
+        <v>4398</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
+          <t>Cuphophyllus virgineus s.lat.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1351,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,7 +1396,7 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128862137</t>
+          <t>https://artportalen.se/Sighting/128862201</t>
         </is>
       </c>
     </row>

--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 4651-2024 artfynd.xlsx
+++ b/artfynd/S 4651-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>128862137</v>
       </c>
       <c r="B6" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
